--- a/hypatia/examples/Neverland/parameters/parameters_connections.xlsx
+++ b/hypatia/examples/Neverland/parameters/parameters_connections.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polimi365-my.sharepoint.com/personal/10394890_polimi_it/Documents/Research/Repositories/Hypatia-polimi/hypatia/examples/Neverland/parameters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_36D1B30646C6E663881BED2D6745987A862E0B96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{970D5BCC-28E6-45F4-9358-27434EC6C553}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_36D1B30646C6E663881BED2D6745987A862E0B96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CC0C8D4-C1B1-484A-8055-A9C1AA7D0CE4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_OM" sheetId="1" r:id="rId1"/>
@@ -2189,6 +2189,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="13.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -2234,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>5</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -2251,10 +2254,10 @@
         <v>0</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>5</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -2268,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>5</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -2285,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>5</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -2302,10 +2305,10 @@
         <v>0</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>5</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2319,10 +2322,10 @@
         <v>0</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>5</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -2336,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>5</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -2353,10 +2356,10 @@
         <v>0</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>5</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -2370,10 +2373,10 @@
         <v>0</v>
       </c>
       <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>5</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -2387,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
         <v>5</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2450,10 +2453,10 @@
         <v>1</v>
       </c>
       <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>0.99</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -2467,10 +2470,10 @@
         <v>1</v>
       </c>
       <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>0.99</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -2484,10 +2487,10 @@
         <v>1</v>
       </c>
       <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>0.99</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -2501,10 +2504,10 @@
         <v>1</v>
       </c>
       <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>0.99</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -2518,10 +2521,10 @@
         <v>1</v>
       </c>
       <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <v>0.99</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2535,10 +2538,10 @@
         <v>1</v>
       </c>
       <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <v>0.99</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -2552,10 +2555,10 @@
         <v>1</v>
       </c>
       <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>0.99</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -2569,10 +2572,10 @@
         <v>1</v>
       </c>
       <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
         <v>0.99</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -2586,10 +2589,10 @@
         <v>1</v>
       </c>
       <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
         <v>0.99</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -2603,10 +2606,10 @@
         <v>1</v>
       </c>
       <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
         <v>0.99</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2666,10 +2669,10 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -2683,10 +2686,10 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -2700,10 +2703,10 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -2717,10 +2720,10 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -2734,10 +2737,10 @@
         <v>100</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2751,10 +2754,10 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -2768,10 +2771,10 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -2785,10 +2788,10 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -2802,10 +2805,10 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -2819,10 +2822,10 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2882,11 +2885,11 @@
         <v>0</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <f>2*10^7</f>
         <v>20000000</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -2900,11 +2903,11 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <f t="shared" ref="D5:D13" si="0">2*10^7</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:E13" si="0">2*10^7</f>
         <v>20000000</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -2918,11 +2921,11 @@
         <v>0</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <f t="shared" si="0"/>
         <v>20000000</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -2936,11 +2939,11 @@
         <v>0</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <f t="shared" si="0"/>
         <v>20000000</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -2954,11 +2957,11 @@
         <v>0</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <f t="shared" si="0"/>
         <v>20000000</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2972,11 +2975,11 @@
         <v>0</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <f t="shared" si="0"/>
         <v>20000000</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -2990,11 +2993,11 @@
         <v>0</v>
       </c>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <f t="shared" si="0"/>
         <v>20000000</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -3008,11 +3011,11 @@
         <v>0</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <f t="shared" si="0"/>
         <v>20000000</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -3026,11 +3029,11 @@
         <v>0</v>
       </c>
       <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <f t="shared" si="0"/>
         <v>20000000</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -3044,11 +3047,11 @@
         <v>0</v>
       </c>
       <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
         <f t="shared" si="0"/>
         <v>20000000</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3327,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3390,7 +3393,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/hypatia/examples/Neverland/parameters/parameters_connections.xlsx
+++ b/hypatia/examples/Neverland/parameters/parameters_connections.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polimi365-my.sharepoint.com/personal/10394890_polimi_it/Documents/Research/Repositories/Hypatia-polimi/hypatia/examples/Neverland/parameters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_36D1B30646C6E663881BED2D6745987A862E0B96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CC0C8D4-C1B1-484A-8055-A9C1AA7D0CE4}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="11_36D1B30646C6E663881BED2D6745987A862E0B96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A00E58AD-560E-446C-B367-89039D3941B0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="13" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_OM" sheetId="1" r:id="rId1"/>
@@ -767,6 +767,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.26953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -1301,13 +1304,13 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1318,13 +1321,13 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1335,13 +1338,13 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1352,13 +1355,13 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1369,13 +1372,13 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1386,13 +1389,13 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1403,13 +1406,13 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1420,13 +1423,13 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1437,13 +1440,13 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1454,13 +1457,13 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
